--- a/BWI/bestwine_output/bestwine_Guadeloupe.xlsx
+++ b/BWI/bestwine_output/bestwine_Guadeloupe.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1945,6 +1945,103 @@
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>La Cave A Vieux</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>La Cave A Vieux</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>90682</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Guadeloupe</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Saint-François</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Grande-Terre, Canton de Saint-François</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Immeuble Trézel</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>97118</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://lacaveavieux.com, https://shopping.lacaveavieux.com</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>lacaveavieux971@gmail.com</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>+590 590 21 99 26</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>79848936500014</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacaveavieux_gp/</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Rosan Kaulanjan</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rosan-kaulanjan-3024ba65/?originalSubdomain=gp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
